--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-careplan</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-careplan</t>
   </si>
   <si>
     <t>Version</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,7 +441,7 @@
     <t>facilityTier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-facility-tier}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-facility-tier}
 </t>
   </si>
   <si>
@@ -461,7 +461,7 @@
     <t>monitoringTrack</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-monitoring-track-ext}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-monitoring-track-ext}
 </t>
   </si>
   <si>
@@ -692,7 +692,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://heartlandprotocol.org/fhir/StructureDefinition/heartland-patient|Patient)
+    <t xml:space="preserve">Reference(https://fhir.heartlandprotocol.org/StructureDefinition/heartland-patient|Patient)
 </t>
   </si>
   <si>
@@ -1314,7 +1314,7 @@
     <t>heartland-distance-to-cardiology</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-distance-to-cardiology</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-distance-to-cardiology</t>
   </si>
   <si>
     <t>HeartlandDistanceToCardiology</t>
@@ -1488,7 +1488,7 @@
     <t>heartland-facility-tier</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-facility-tier</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-facility-tier</t>
   </si>
   <si>
     <t>HeartlandFacilityTier</t>
@@ -1503,25 +1503,25 @@
     <t>element:CarePlan</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-implementation-tier-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-implementation-tier-vs</t>
   </si>
   <si>
     <t>heartland-monitoring-track-ext</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-monitoring-track-ext</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-monitoring-track-ext</t>
   </si>
   <si>
     <t>HeartlandMonitoringTrackExtension</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-monitoring-track-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-monitoring-track-vs</t>
   </si>
   <si>
     <t>heartland-patient</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-patient</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-patient</t>
   </si>
   <si>
     <t>HeartlandPatient</t>
@@ -1576,7 +1576,7 @@
     <t>distanceToCardiology</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-distance-to-cardiology}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-distance-to-cardiology}
 </t>
   </si>
   <si>
@@ -1586,7 +1586,7 @@
     <t>socialSupportScore</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-social-support-score}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-social-support-score}
 </t>
   </si>
   <si>
@@ -2078,7 +2078,7 @@
     <t>heartland-questionnaire-response</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-questionnaire-response</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-questionnaire-response</t>
   </si>
   <si>
     <t>HeartlandQuestionnaireResponse</t>
@@ -2459,7 +2459,7 @@
     <t>heartland-remote-monitoring-observation</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-remote-monitoring-observation</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-remote-monitoring-observation</t>
   </si>
   <si>
     <t>HeartlandRemoteMonitoringObservation</t>
@@ -2646,7 +2646,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-monitoring-observation-code-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-monitoring-observation-code-vs</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -3139,7 +3139,7 @@
     <t>heartland-risk-assessment</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-risk-assessment</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-risk-assessment</t>
   </si>
   <si>
     <t>HeartlandRiskAssessment</t>
@@ -3455,7 +3455,7 @@
     <t>Indicates how likely the outcome is (in the specified timeframe), expressed as a qualitative value (e.g. low, medium, or high).</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-risk-tier-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-risk-tier-vs</t>
   </si>
   <si>
     <t>RiskAssessment.prediction.relativeRisk</t>
@@ -3519,7 +3519,7 @@
     <t>heartland-social-support-score</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-social-support-score</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-social-support-score</t>
   </si>
   <si>
     <t>HeartlandSocialSupportScore</t>
@@ -5295,7 +5295,7 @@
     <col min="24" max="24" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="138.09375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="71.24609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="70.984375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.1015625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="35.91015625" customWidth="true" bestFit="true"/>
